--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S439"/>
+  <dimension ref="A1:S440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28109,6 +28109,69 @@
         <v>284.98</v>
       </c>
       <c r="S439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="C440" t="n">
+        <v>260.47</v>
+      </c>
+      <c r="D440" t="n">
+        <v>255.59</v>
+      </c>
+      <c r="E440" t="n">
+        <v>259.89</v>
+      </c>
+      <c r="F440" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="G440" t="n">
+        <v>255.91</v>
+      </c>
+      <c r="H440" t="n">
+        <v>260.98</v>
+      </c>
+      <c r="I440" t="n">
+        <v>264.43</v>
+      </c>
+      <c r="J440" t="n">
+        <v>264.84</v>
+      </c>
+      <c r="K440" t="n">
+        <v>268.79</v>
+      </c>
+      <c r="L440" t="n">
+        <v>268.85</v>
+      </c>
+      <c r="M440" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="N440" t="n">
+        <v>275.64</v>
+      </c>
+      <c r="O440" t="n">
+        <v>285.96</v>
+      </c>
+      <c r="P440" t="n">
+        <v>281.94</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>280.23</v>
+      </c>
+      <c r="R440" t="n">
+        <v>284.31</v>
+      </c>
+      <c r="S440" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28125,7 +28188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B452"/>
+  <dimension ref="A1:B453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32648,6 +32711,16 @@
       </c>
       <c r="B452" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -32810,28 +32883,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4369746846607107</v>
+        <v>-0.4361980912356568</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K2" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.204396451979488</v>
+        <v>0.2046897604878147</v>
       </c>
       <c r="M2" t="n">
-        <v>4.564698494655612</v>
+        <v>4.557845096176568</v>
       </c>
       <c r="N2" t="n">
-        <v>39.44515989847743</v>
+        <v>39.36112136459464</v>
       </c>
       <c r="O2" t="n">
-        <v>6.28053818541671</v>
+        <v>6.273844225400775</v>
       </c>
       <c r="P2" t="n">
-        <v>274.172142401979</v>
+        <v>274.1641055916111</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32882,28 +32955,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3244382685928031</v>
+        <v>-0.3244016579627897</v>
       </c>
       <c r="J3" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K3" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1009961097980546</v>
+        <v>0.1014767077739561</v>
       </c>
       <c r="M3" t="n">
-        <v>5.207365683230071</v>
+        <v>5.195648245639062</v>
       </c>
       <c r="N3" t="n">
-        <v>49.7254683829259</v>
+        <v>49.61221144394009</v>
       </c>
       <c r="O3" t="n">
-        <v>7.051628775178534</v>
+        <v>7.043593645571846</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9463970370555</v>
+        <v>268.946018160952</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32954,28 +33027,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.373945627063588</v>
+        <v>-0.3739459730436999</v>
       </c>
       <c r="J4" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K4" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1086068666339307</v>
+        <v>0.1091414330087132</v>
       </c>
       <c r="M4" t="n">
-        <v>5.41307113788722</v>
+        <v>5.400742460186655</v>
       </c>
       <c r="N4" t="n">
-        <v>60.90973711939612</v>
+        <v>60.77099056674729</v>
       </c>
       <c r="O4" t="n">
-        <v>7.804469047885072</v>
+        <v>7.795575063248849</v>
       </c>
       <c r="P4" t="n">
-        <v>265.45077670912</v>
+        <v>265.4507802895991</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33026,28 +33099,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3073171065838534</v>
+        <v>-0.3059026305573033</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K5" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08728754390933413</v>
+        <v>0.08696245944804781</v>
       </c>
       <c r="M5" t="n">
-        <v>4.770062707800344</v>
+        <v>4.765172344773476</v>
       </c>
       <c r="N5" t="n">
-        <v>52.40985793567295</v>
+        <v>52.30976014571946</v>
       </c>
       <c r="O5" t="n">
-        <v>7.239465307305019</v>
+        <v>7.232548661828655</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0718506960386</v>
+        <v>265.0572125659327</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33098,28 +33171,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3931549606839892</v>
+        <v>-0.3933402840816217</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K6" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2057743321658245</v>
+        <v>0.2068288291162921</v>
       </c>
       <c r="M6" t="n">
-        <v>4.296424737790516</v>
+        <v>4.287346258488635</v>
       </c>
       <c r="N6" t="n">
-        <v>31.66197812317321</v>
+        <v>31.59018624444429</v>
       </c>
       <c r="O6" t="n">
-        <v>5.626897735268805</v>
+        <v>5.620514766855816</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6493579031651</v>
+        <v>267.6512757780214</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33170,28 +33243,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6252673312830758</v>
+        <v>-0.6255040191170269</v>
       </c>
       <c r="J7" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K7" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2870885602711559</v>
+        <v>0.2883703457639268</v>
       </c>
       <c r="M7" t="n">
-        <v>5.211632016107855</v>
+        <v>5.200796819263354</v>
       </c>
       <c r="N7" t="n">
-        <v>51.52392986953899</v>
+        <v>51.40710332185983</v>
       </c>
       <c r="O7" t="n">
-        <v>7.178017126584401</v>
+        <v>7.169874707542652</v>
       </c>
       <c r="P7" t="n">
-        <v>272.8927152768471</v>
+        <v>272.8951647120039</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33242,28 +33315,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.468684040542438</v>
+        <v>-0.4665812399061878</v>
       </c>
       <c r="J8" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K8" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1894897435226262</v>
+        <v>0.1888238103982819</v>
       </c>
       <c r="M8" t="n">
-        <v>5.274978747206106</v>
+        <v>5.273255604981407</v>
       </c>
       <c r="N8" t="n">
-        <v>49.86443986217368</v>
+        <v>49.79347863304563</v>
       </c>
       <c r="O8" t="n">
-        <v>7.061475756679596</v>
+        <v>7.056449435307082</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9949882313675</v>
+        <v>268.9732267672478</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33314,28 +33387,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.200133134748082</v>
+        <v>-0.1977050295066627</v>
       </c>
       <c r="J9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04355479301416243</v>
+        <v>0.04272409349518291</v>
       </c>
       <c r="M9" t="n">
-        <v>5.147923932342698</v>
+        <v>5.147958614096629</v>
       </c>
       <c r="N9" t="n">
-        <v>46.67882807193413</v>
+        <v>46.62933176982101</v>
       </c>
       <c r="O9" t="n">
-        <v>6.83219057637696</v>
+        <v>6.828567329229537</v>
       </c>
       <c r="P9" t="n">
-        <v>264.6912243703529</v>
+        <v>264.6660963937967</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33386,28 +33459,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2857456916027966</v>
+        <v>-0.2844461026118538</v>
       </c>
       <c r="J10" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K10" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07236447685189618</v>
+        <v>0.07210293977781546</v>
       </c>
       <c r="M10" t="n">
-        <v>5.74778588289972</v>
+        <v>5.741733625756066</v>
       </c>
       <c r="N10" t="n">
-        <v>55.5480904010492</v>
+        <v>55.43783820835085</v>
       </c>
       <c r="O10" t="n">
-        <v>7.45305913038728</v>
+        <v>7.445659017733142</v>
       </c>
       <c r="P10" t="n">
-        <v>269.6905041511343</v>
+        <v>269.6770549640316</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33458,28 +33531,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1103015088965919</v>
+        <v>0.1112556114216994</v>
       </c>
       <c r="J11" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K11" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0103572970150928</v>
+        <v>0.01059143464836509</v>
       </c>
       <c r="M11" t="n">
-        <v>6.158119773728495</v>
+        <v>6.148648275210197</v>
       </c>
       <c r="N11" t="n">
-        <v>61.69538950449354</v>
+        <v>61.56362857516173</v>
       </c>
       <c r="O11" t="n">
-        <v>7.854641271534527</v>
+        <v>7.84624933169739</v>
       </c>
       <c r="P11" t="n">
-        <v>263.9075113600646</v>
+        <v>263.8976375434466</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33530,28 +33603,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05999627217116611</v>
+        <v>-0.05735988018539869</v>
       </c>
       <c r="J12" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K12" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004605965393547184</v>
+        <v>0.004228045690208293</v>
       </c>
       <c r="M12" t="n">
-        <v>5.275497283008427</v>
+        <v>5.277624462734813</v>
       </c>
       <c r="N12" t="n">
-        <v>41.28389868329847</v>
+        <v>41.2568602775536</v>
       </c>
       <c r="O12" t="n">
-        <v>6.425254756295542</v>
+        <v>6.423150339012283</v>
       </c>
       <c r="P12" t="n">
-        <v>264.9897500669111</v>
+        <v>264.9624665724063</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33602,28 +33675,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1001897288764527</v>
+        <v>-0.09775785028886635</v>
       </c>
       <c r="J13" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K13" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007289087618732482</v>
+        <v>0.006974575967166552</v>
       </c>
       <c r="M13" t="n">
-        <v>6.624351894751898</v>
+        <v>6.621098896423418</v>
       </c>
       <c r="N13" t="n">
-        <v>72.55274278237643</v>
+        <v>72.44448495735733</v>
       </c>
       <c r="O13" t="n">
-        <v>8.517789782706334</v>
+        <v>8.511432603114315</v>
       </c>
       <c r="P13" t="n">
-        <v>271.247604061214</v>
+        <v>271.2224370350514</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33674,28 +33747,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0110866262381007</v>
+        <v>-0.009504249483440506</v>
       </c>
       <c r="J14" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K14" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000102310751946999</v>
+        <v>7.557828668802724e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>6.211743581001464</v>
+        <v>6.205995683972628</v>
       </c>
       <c r="N14" t="n">
-        <v>63.75157349018574</v>
+        <v>63.63049087572502</v>
       </c>
       <c r="O14" t="n">
-        <v>7.984458246505253</v>
+        <v>7.976872248928462</v>
       </c>
       <c r="P14" t="n">
-        <v>272.6689116570496</v>
+        <v>272.6525359558173</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33746,28 +33819,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2622000038952493</v>
+        <v>-0.2591576146561446</v>
       </c>
       <c r="J15" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K15" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05264892538107468</v>
+        <v>0.05169968555387405</v>
       </c>
       <c r="M15" t="n">
-        <v>6.036052373923511</v>
+        <v>6.039158016646262</v>
       </c>
       <c r="N15" t="n">
-        <v>65.65149734965216</v>
+        <v>65.59117722500474</v>
       </c>
       <c r="O15" t="n">
-        <v>8.10256115988347</v>
+        <v>8.098838016962974</v>
       </c>
       <c r="P15" t="n">
-        <v>286.5924905465628</v>
+        <v>286.5610054675099</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33818,28 +33891,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4330882025201744</v>
+        <v>-0.4301744552394872</v>
       </c>
       <c r="J16" t="n">
+        <v>439</v>
+      </c>
+      <c r="K16" t="n">
         <v>438</v>
       </c>
-      <c r="K16" t="n">
-        <v>437</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1340548245290355</v>
+        <v>0.1329818571456436</v>
       </c>
       <c r="M16" t="n">
-        <v>6.207497029226057</v>
+        <v>6.206840532271603</v>
       </c>
       <c r="N16" t="n">
-        <v>64.38990004700867</v>
+        <v>64.32492268046167</v>
       </c>
       <c r="O16" t="n">
-        <v>8.024331750806958</v>
+        <v>8.020281957665931</v>
       </c>
       <c r="P16" t="n">
-        <v>287.3434233372185</v>
+        <v>287.3132704485496</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33890,28 +33963,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2172627038479144</v>
+        <v>-0.2140662169753681</v>
       </c>
       <c r="J17" t="n">
+        <v>439</v>
+      </c>
+      <c r="K17" t="n">
         <v>438</v>
       </c>
-      <c r="K17" t="n">
-        <v>437</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.03982201600623636</v>
+        <v>0.03884806481587622</v>
       </c>
       <c r="M17" t="n">
-        <v>6.496849328879247</v>
+        <v>6.498545289599468</v>
       </c>
       <c r="N17" t="n">
-        <v>60.48615203030469</v>
+        <v>60.44677983758087</v>
       </c>
       <c r="O17" t="n">
-        <v>7.777284360900319</v>
+        <v>7.774752718741662</v>
       </c>
       <c r="P17" t="n">
-        <v>279.359223522635</v>
+        <v>279.326144705732</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33962,28 +34035,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1796406113251841</v>
+        <v>0.1871213257046959</v>
       </c>
       <c r="J18" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K18" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02402083371344887</v>
+        <v>0.0259528731266444</v>
       </c>
       <c r="M18" t="n">
-        <v>6.43762496144628</v>
+        <v>6.465401551322862</v>
       </c>
       <c r="N18" t="n">
-        <v>69.81408584294759</v>
+        <v>70.19651068427156</v>
       </c>
       <c r="O18" t="n">
-        <v>8.355482382420993</v>
+        <v>8.37833579443266</v>
       </c>
       <c r="P18" t="n">
-        <v>264.11569859528</v>
+        <v>264.0383208611394</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34021,7 +34094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S439"/>
+  <dimension ref="A1:S440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76591,6 +76664,103 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-40.83297536816288,172.8756631135645</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-40.83299215749327,172.87471348077227</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-40.833021219521,172.8737475329482</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-40.832982487613755,172.87279867266102</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-40.83300941977595,172.87184984809946</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-40.83298360911226,172.87095216576762</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-40.83288495540443,172.87000969025112</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-40.832794496870406,172.86911548918485</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-40.8326935652595,172.86817527944058</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-40.83256110142006,172.86724145068206</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-40.832438920318936,172.86635596048427</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-40.83225715808312,172.8654360420785</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-40.83210034078354,172.8645261693644</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-40.831857489721216,172.86362451410685</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-40.831740761654835,172.86268610383487</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-40.83161712587126,172.86172591107447</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>-40.83144747815349,172.86080247487803</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S440"/>
+  <dimension ref="A1:S441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28174,6 +28174,69 @@
       <c r="S440" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>263.68</v>
+      </c>
+      <c r="C441" t="n">
+        <v>260.29</v>
+      </c>
+      <c r="D441" t="n">
+        <v>254.94</v>
+      </c>
+      <c r="E441" t="n">
+        <v>258.88</v>
+      </c>
+      <c r="F441" t="n">
+        <v>255.91</v>
+      </c>
+      <c r="G441" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="H441" t="n">
+        <v>257.3</v>
+      </c>
+      <c r="I441" t="n">
+        <v>261.02</v>
+      </c>
+      <c r="J441" t="n">
+        <v>263.59</v>
+      </c>
+      <c r="K441" t="n">
+        <v>266.32</v>
+      </c>
+      <c r="L441" t="n">
+        <v>267.04</v>
+      </c>
+      <c r="M441" t="n">
+        <v>271.79</v>
+      </c>
+      <c r="N441" t="n">
+        <v>275.02</v>
+      </c>
+      <c r="O441" t="n">
+        <v>284.78</v>
+      </c>
+      <c r="P441" t="n">
+        <v>281.74</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>280.02</v>
+      </c>
+      <c r="R441" t="n">
+        <v>280.83</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28188,7 +28251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B453"/>
+  <dimension ref="A1:B454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32721,6 +32784,16 @@
       </c>
       <c r="B453" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>
@@ -32883,28 +32956,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4361980912356568</v>
+        <v>-0.4356913371680254</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2046897604878147</v>
+        <v>0.2051994943637667</v>
       </c>
       <c r="M2" t="n">
-        <v>4.557845096176568</v>
+        <v>4.549779842491459</v>
       </c>
       <c r="N2" t="n">
-        <v>39.36112136459464</v>
+        <v>39.27414405919272</v>
       </c>
       <c r="O2" t="n">
-        <v>6.273844225400775</v>
+        <v>6.26690865253298</v>
       </c>
       <c r="P2" t="n">
-        <v>274.1641055916111</v>
+        <v>274.1588475344442</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32955,28 +33028,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3244016579627897</v>
+        <v>-0.3244418867342714</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1014767077739561</v>
+        <v>0.1020034726672912</v>
       </c>
       <c r="M3" t="n">
-        <v>5.195648245639062</v>
+        <v>5.184058104930103</v>
       </c>
       <c r="N3" t="n">
-        <v>49.61221144394009</v>
+        <v>49.49947204558248</v>
       </c>
       <c r="O3" t="n">
-        <v>7.043593645571846</v>
+        <v>7.035586119548426</v>
       </c>
       <c r="P3" t="n">
-        <v>268.946018160952</v>
+        <v>268.9464355728559</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33027,28 +33100,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3739459730436999</v>
+        <v>-0.3742468759228877</v>
       </c>
       <c r="J4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1091414330087132</v>
+        <v>0.1098347155040351</v>
       </c>
       <c r="M4" t="n">
-        <v>5.400742460186655</v>
+        <v>5.390024064216703</v>
       </c>
       <c r="N4" t="n">
-        <v>60.77099056674729</v>
+        <v>60.63374900402295</v>
       </c>
       <c r="O4" t="n">
-        <v>7.795575063248849</v>
+        <v>7.786767558109267</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4507802895991</v>
+        <v>265.4539024441934</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33099,28 +33172,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3059026305573033</v>
+        <v>-0.3049775532587638</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08696245944804781</v>
+        <v>0.08690694616302519</v>
       </c>
       <c r="M5" t="n">
-        <v>4.765172344773476</v>
+        <v>4.758244378172222</v>
       </c>
       <c r="N5" t="n">
-        <v>52.30976014571946</v>
+        <v>52.19913805914183</v>
       </c>
       <c r="O5" t="n">
-        <v>7.232548661828655</v>
+        <v>7.224897096785658</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0572125659327</v>
+        <v>265.0476140059405</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33171,28 +33244,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3933402840816217</v>
+        <v>-0.3939896619800336</v>
       </c>
       <c r="J6" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K6" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2068288291162921</v>
+        <v>0.208257444860233</v>
       </c>
       <c r="M6" t="n">
-        <v>4.287346258488635</v>
+        <v>4.28006411052069</v>
       </c>
       <c r="N6" t="n">
-        <v>31.59018624444429</v>
+        <v>31.52246243610468</v>
       </c>
       <c r="O6" t="n">
-        <v>5.620514766855816</v>
+        <v>5.614486836399626</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6512757780214</v>
+        <v>267.6580136935723</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33243,28 +33316,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6255040191170269</v>
+        <v>-0.6265492451501202</v>
       </c>
       <c r="J7" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K7" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2883703457639268</v>
+        <v>0.2901486570911215</v>
       </c>
       <c r="M7" t="n">
-        <v>5.200796819263354</v>
+        <v>5.193518075185212</v>
       </c>
       <c r="N7" t="n">
-        <v>51.40710332185983</v>
+        <v>51.30081870827506</v>
       </c>
       <c r="O7" t="n">
-        <v>7.169874707542652</v>
+        <v>7.162458984753425</v>
       </c>
       <c r="P7" t="n">
-        <v>272.8951647120039</v>
+        <v>272.9060099298034</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33315,28 +33388,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4665812399061878</v>
+        <v>-0.4662634376970773</v>
       </c>
       <c r="J8" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K8" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1888238103982819</v>
+        <v>0.1894578201253516</v>
       </c>
       <c r="M8" t="n">
-        <v>5.273255604981407</v>
+        <v>5.262813831324739</v>
       </c>
       <c r="N8" t="n">
-        <v>49.79347863304563</v>
+        <v>49.68128692666009</v>
       </c>
       <c r="O8" t="n">
-        <v>7.056449435307082</v>
+        <v>7.048495366151566</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9732267672478</v>
+        <v>268.9699292659745</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33387,28 +33460,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1977050295066627</v>
+        <v>-0.1969392866157891</v>
       </c>
       <c r="J9" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K9" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04272409349518291</v>
+        <v>0.04262740111872121</v>
       </c>
       <c r="M9" t="n">
-        <v>5.147958614096629</v>
+        <v>5.139985661475048</v>
       </c>
       <c r="N9" t="n">
-        <v>46.62933176982101</v>
+        <v>46.52901822773436</v>
       </c>
       <c r="O9" t="n">
-        <v>6.828567329229537</v>
+        <v>6.821218236336847</v>
       </c>
       <c r="P9" t="n">
-        <v>264.6660963937967</v>
+        <v>264.6581510803745</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33459,28 +33532,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2844461026118538</v>
+        <v>-0.2837527563111628</v>
       </c>
       <c r="J10" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K10" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07210293977781546</v>
+        <v>0.07213983738087859</v>
       </c>
       <c r="M10" t="n">
-        <v>5.741733625756066</v>
+        <v>5.73244123857652</v>
       </c>
       <c r="N10" t="n">
-        <v>55.43783820835085</v>
+        <v>55.31648528658304</v>
       </c>
       <c r="O10" t="n">
-        <v>7.445659017733142</v>
+        <v>7.437505313381836</v>
       </c>
       <c r="P10" t="n">
-        <v>269.6770549640316</v>
+        <v>269.6698608343377</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33531,28 +33604,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1112556114216994</v>
+        <v>0.1110054058481351</v>
       </c>
       <c r="J11" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K11" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01059143464836509</v>
+        <v>0.01060195626628613</v>
       </c>
       <c r="M11" t="n">
-        <v>6.148648275210197</v>
+        <v>6.13582413870422</v>
       </c>
       <c r="N11" t="n">
-        <v>61.56362857516173</v>
+        <v>61.42431576230677</v>
       </c>
       <c r="O11" t="n">
-        <v>7.84624933169739</v>
+        <v>7.837366634419164</v>
       </c>
       <c r="P11" t="n">
-        <v>263.8976375434466</v>
+        <v>263.9002336651026</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33603,28 +33676,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05735988018539869</v>
+        <v>-0.05562203631772406</v>
       </c>
       <c r="J12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004228045690208293</v>
+        <v>0.003995824045348928</v>
       </c>
       <c r="M12" t="n">
-        <v>5.277624462734813</v>
+        <v>5.274884809828441</v>
       </c>
       <c r="N12" t="n">
-        <v>41.2568602775536</v>
+        <v>41.1922583231083</v>
       </c>
       <c r="O12" t="n">
-        <v>6.423150339012283</v>
+        <v>6.418119531693711</v>
       </c>
       <c r="P12" t="n">
-        <v>264.9624665724063</v>
+        <v>264.944434783444</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33675,28 +33748,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09775785028886635</v>
+        <v>-0.09623305715418952</v>
       </c>
       <c r="J13" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K13" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006974575967166552</v>
+        <v>0.006795201725059652</v>
       </c>
       <c r="M13" t="n">
-        <v>6.621098896423418</v>
+        <v>6.613413331541238</v>
       </c>
       <c r="N13" t="n">
-        <v>72.44448495735733</v>
+        <v>72.30228972837608</v>
       </c>
       <c r="O13" t="n">
-        <v>8.511432603114315</v>
+        <v>8.503075310049658</v>
       </c>
       <c r="P13" t="n">
-        <v>271.2224370350514</v>
+        <v>271.2066158508086</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33747,28 +33820,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.009504249483440506</v>
+        <v>-0.008240899077111393</v>
       </c>
       <c r="J14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L14" t="n">
-        <v>7.557828668802724e-05</v>
+        <v>5.712271955082837e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>6.205995683972628</v>
+        <v>6.198588961443684</v>
       </c>
       <c r="N14" t="n">
-        <v>63.63049087572502</v>
+        <v>63.50128843681723</v>
       </c>
       <c r="O14" t="n">
-        <v>7.976872248928462</v>
+        <v>7.968769568560583</v>
       </c>
       <c r="P14" t="n">
-        <v>272.6525359558173</v>
+        <v>272.6394274894377</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33819,28 +33892,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2591576146561446</v>
+        <v>-0.2567058002947259</v>
       </c>
       <c r="J15" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K15" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05169968555387405</v>
+        <v>0.05099911955396763</v>
       </c>
       <c r="M15" t="n">
-        <v>6.039158016646262</v>
+        <v>6.038917942801119</v>
       </c>
       <c r="N15" t="n">
-        <v>65.59117722500474</v>
+        <v>65.50015544792559</v>
       </c>
       <c r="O15" t="n">
-        <v>8.098838016962974</v>
+        <v>8.093216631718541</v>
       </c>
       <c r="P15" t="n">
-        <v>286.5610054675099</v>
+        <v>286.5355655531642</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33891,28 +33964,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4301744552394872</v>
+        <v>-0.4273704607247127</v>
       </c>
       <c r="J16" t="n">
+        <v>440</v>
+      </c>
+      <c r="K16" t="n">
         <v>439</v>
       </c>
-      <c r="K16" t="n">
-        <v>438</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1329818571456436</v>
+        <v>0.1319758800878265</v>
       </c>
       <c r="M16" t="n">
-        <v>6.206840532271603</v>
+        <v>6.20566859325702</v>
       </c>
       <c r="N16" t="n">
-        <v>64.32492268046167</v>
+        <v>64.25449488002899</v>
       </c>
       <c r="O16" t="n">
-        <v>8.020281957665931</v>
+        <v>8.015890148949708</v>
       </c>
       <c r="P16" t="n">
-        <v>287.3132704485496</v>
+        <v>287.2841769495738</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33963,28 +34036,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2140662169753681</v>
+        <v>-0.210996145624771</v>
       </c>
       <c r="J17" t="n">
+        <v>440</v>
+      </c>
+      <c r="K17" t="n">
         <v>439</v>
       </c>
-      <c r="K17" t="n">
-        <v>438</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.03884806481587622</v>
+        <v>0.03792924091978989</v>
       </c>
       <c r="M17" t="n">
-        <v>6.498545289599468</v>
+        <v>6.499499401859097</v>
       </c>
       <c r="N17" t="n">
-        <v>60.44677983758087</v>
+        <v>60.40031353694781</v>
       </c>
       <c r="O17" t="n">
-        <v>7.774752718741662</v>
+        <v>7.771763862659995</v>
       </c>
       <c r="P17" t="n">
-        <v>279.326144705732</v>
+        <v>279.2942904644973</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34035,28 +34108,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1871213257046959</v>
+        <v>0.1928447057101781</v>
       </c>
       <c r="J18" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K18" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0259528731266444</v>
+        <v>0.02754658216969963</v>
       </c>
       <c r="M18" t="n">
-        <v>6.465401551322862</v>
+        <v>6.482944759184867</v>
       </c>
       <c r="N18" t="n">
-        <v>70.19651068427156</v>
+        <v>70.35415365344218</v>
       </c>
       <c r="O18" t="n">
-        <v>8.37833579443266</v>
+        <v>8.387738291902185</v>
       </c>
       <c r="P18" t="n">
-        <v>264.0383208611394</v>
+        <v>263.978963939934</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34094,7 +34167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S440"/>
+  <dimension ref="A1:S441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76761,6 +76834,103 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-40.832980501550644,172.87566295286973</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-40.832993778562646,172.87471343000342</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-40.83302707503786,172.87374753620028</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-40.83299158618601,172.87279867758457</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-40.83301833817826,172.8718498527984</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-40.83299897127024,172.8709506628025</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-40.83291801772838,172.87000649576655</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-40.83282493223108,172.86911000638443</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-40.832704723304396,172.86817328301876</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-40.8325831495919,172.86723750455042</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-40.83245491797421,172.86635180962995</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-40.832273420859444,172.8654318222124</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-40.832105800250865,172.86452461749863</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-40.83186788029745,172.86362156042583</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-40.83174252311098,172.86268560529902</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-40.83161898499021,172.86172545024436</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-40.83147828634918,172.86079483785363</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S441"/>
+  <dimension ref="A1:S444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28237,6 +28237,195 @@
       <c r="S441" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:13:02+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>262.14</v>
+      </c>
+      <c r="C442" t="n">
+        <v>259.19</v>
+      </c>
+      <c r="D442" t="n">
+        <v>254.03</v>
+      </c>
+      <c r="E442" t="n">
+        <v>257.17</v>
+      </c>
+      <c r="F442" t="n">
+        <v>254.53</v>
+      </c>
+      <c r="G442" t="n">
+        <v>254.21</v>
+      </c>
+      <c r="H442" t="n">
+        <v>257.27</v>
+      </c>
+      <c r="I442" t="n">
+        <v>259.57</v>
+      </c>
+      <c r="J442" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="K442" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="L442" t="n">
+        <v>265.85</v>
+      </c>
+      <c r="M442" t="n">
+        <v>270.34</v>
+      </c>
+      <c r="N442" t="n">
+        <v>274.66</v>
+      </c>
+      <c r="O442" t="n">
+        <v>283.64</v>
+      </c>
+      <c r="P442" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>279.87</v>
+      </c>
+      <c r="R442" t="n">
+        <v>279.49</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>262.15</v>
+      </c>
+      <c r="C443" t="n">
+        <v>258.73</v>
+      </c>
+      <c r="D443" t="n">
+        <v>253.65</v>
+      </c>
+      <c r="E443" t="n">
+        <v>257.53</v>
+      </c>
+      <c r="F443" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="G443" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="H443" t="n">
+        <v>256.69</v>
+      </c>
+      <c r="I443" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="J443" t="n">
+        <v>263.45</v>
+      </c>
+      <c r="K443" t="n">
+        <v>265.88</v>
+      </c>
+      <c r="L443" t="n">
+        <v>265.97</v>
+      </c>
+      <c r="M443" t="n">
+        <v>269.91</v>
+      </c>
+      <c r="N443" t="n">
+        <v>274.87</v>
+      </c>
+      <c r="O443" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="P443" t="n">
+        <v>280.88</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>281.44</v>
+      </c>
+      <c r="R443" t="n">
+        <v>277.81</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>263.52</v>
+      </c>
+      <c r="C444" t="n">
+        <v>259.69</v>
+      </c>
+      <c r="D444" t="n">
+        <v>254.29</v>
+      </c>
+      <c r="E444" t="n">
+        <v>258.22</v>
+      </c>
+      <c r="F444" t="n">
+        <v>255.06</v>
+      </c>
+      <c r="G444" t="n">
+        <v>255.03</v>
+      </c>
+      <c r="H444" t="n">
+        <v>257.86</v>
+      </c>
+      <c r="I444" t="n">
+        <v>261.47</v>
+      </c>
+      <c r="J444" t="n">
+        <v>265.31</v>
+      </c>
+      <c r="K444" t="n">
+        <v>269.09</v>
+      </c>
+      <c r="L444" t="n">
+        <v>266.32</v>
+      </c>
+      <c r="M444" t="n">
+        <v>268.83</v>
+      </c>
+      <c r="N444" t="n">
+        <v>274.02</v>
+      </c>
+      <c r="O444" t="n">
+        <v>283.86</v>
+      </c>
+      <c r="P444" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>282.13</v>
+      </c>
+      <c r="R444" t="n">
+        <v>278.62</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28251,7 +28440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B454"/>
+  <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32794,6 +32983,36 @@
       </c>
       <c r="B454" t="n">
         <v>1.82</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -32956,28 +33175,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4356913371680254</v>
+        <v>-0.4356912854564569</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K2" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2051994943637667</v>
+        <v>0.2078831302333494</v>
       </c>
       <c r="M2" t="n">
-        <v>4.549779842491459</v>
+        <v>4.523156924940015</v>
       </c>
       <c r="N2" t="n">
-        <v>39.27414405919272</v>
+        <v>39.01109122751026</v>
       </c>
       <c r="O2" t="n">
-        <v>6.26690865253298</v>
+        <v>6.245885944164387</v>
       </c>
       <c r="P2" t="n">
-        <v>274.1588475344442</v>
+        <v>274.158838780056</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33028,28 +33247,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3244418867342714</v>
+        <v>-0.3260684201266394</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K3" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1020034726672912</v>
+        <v>0.1044336903763358</v>
       </c>
       <c r="M3" t="n">
-        <v>5.184058104930103</v>
+        <v>5.157672202620083</v>
       </c>
       <c r="N3" t="n">
-        <v>49.49947204558248</v>
+        <v>49.17393217400938</v>
       </c>
       <c r="O3" t="n">
-        <v>7.035586119548426</v>
+        <v>7.012412721311359</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9464355728559</v>
+        <v>268.9633637197273</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33100,28 +33319,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3742468759228877</v>
+        <v>-0.3764454966297421</v>
       </c>
       <c r="J4" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1098347155040351</v>
+        <v>0.112592050097906</v>
       </c>
       <c r="M4" t="n">
-        <v>5.390024064216703</v>
+        <v>5.364787200093733</v>
       </c>
       <c r="N4" t="n">
-        <v>60.63374900402295</v>
+        <v>60.23933060561504</v>
       </c>
       <c r="O4" t="n">
-        <v>7.786767558109267</v>
+        <v>7.761400041591403</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4539024441934</v>
+        <v>265.4767867447653</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33172,28 +33391,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3049775532587638</v>
+        <v>-0.3040089993517033</v>
       </c>
       <c r="J5" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08690694616302519</v>
+        <v>0.08770410701987086</v>
       </c>
       <c r="M5" t="n">
-        <v>4.758244378172222</v>
+        <v>4.730083864431723</v>
       </c>
       <c r="N5" t="n">
-        <v>52.19913805914183</v>
+        <v>51.8500292105148</v>
       </c>
       <c r="O5" t="n">
-        <v>7.224897096785658</v>
+        <v>7.20069643926994</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0476140059405</v>
+        <v>265.0375255738525</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33244,28 +33463,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3939896619800336</v>
+        <v>-0.3976019423920919</v>
       </c>
       <c r="J6" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K6" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L6" t="n">
-        <v>0.208257444860233</v>
+        <v>0.2138069333734505</v>
       </c>
       <c r="M6" t="n">
-        <v>4.28006411052069</v>
+        <v>4.264591731664714</v>
       </c>
       <c r="N6" t="n">
-        <v>31.52246243610468</v>
+        <v>31.3519643516739</v>
       </c>
       <c r="O6" t="n">
-        <v>5.614486836399626</v>
+        <v>5.599282485432745</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6580136935723</v>
+        <v>267.6956107020047</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33316,28 +33535,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6265492451501202</v>
+        <v>-0.6290165601148299</v>
       </c>
       <c r="J7" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K7" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2901486570911215</v>
+        <v>0.295096816318314</v>
       </c>
       <c r="M7" t="n">
-        <v>5.193518075185212</v>
+        <v>5.168927767626548</v>
       </c>
       <c r="N7" t="n">
-        <v>51.30081870827506</v>
+        <v>50.9740855385384</v>
       </c>
       <c r="O7" t="n">
-        <v>7.162458984753425</v>
+        <v>7.139613822787505</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9060099298034</v>
+        <v>272.9316868222296</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33388,28 +33607,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4662634376970773</v>
+        <v>-0.4653104842770403</v>
       </c>
       <c r="J8" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K8" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1894578201253516</v>
+        <v>0.1913488101348971</v>
       </c>
       <c r="M8" t="n">
-        <v>5.262813831324739</v>
+        <v>5.231778338245679</v>
       </c>
       <c r="N8" t="n">
-        <v>49.68128692666009</v>
+        <v>49.34935456780887</v>
       </c>
       <c r="O8" t="n">
-        <v>7.048495366151566</v>
+        <v>7.024909577198049</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9699292659745</v>
+        <v>268.9600071930385</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33460,28 +33679,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1969392866157891</v>
+        <v>-0.1957309273480155</v>
       </c>
       <c r="J9" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K9" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04262740111872121</v>
+        <v>0.04278818308772647</v>
       </c>
       <c r="M9" t="n">
-        <v>5.139985661475048</v>
+        <v>5.110997897253712</v>
       </c>
       <c r="N9" t="n">
-        <v>46.52901822773436</v>
+        <v>46.2235663690602</v>
       </c>
       <c r="O9" t="n">
-        <v>6.821218236336847</v>
+        <v>6.79879153740282</v>
       </c>
       <c r="P9" t="n">
-        <v>264.6581510803745</v>
+        <v>264.6455618765343</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33532,28 +33751,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2837527563111628</v>
+        <v>-0.2810731486862204</v>
       </c>
       <c r="J10" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K10" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07213983738087859</v>
+        <v>0.07193568922593074</v>
       </c>
       <c r="M10" t="n">
-        <v>5.73244123857652</v>
+        <v>5.708119066814568</v>
       </c>
       <c r="N10" t="n">
-        <v>55.31648528658304</v>
+        <v>54.97088355738071</v>
       </c>
       <c r="O10" t="n">
-        <v>7.437505313381836</v>
+        <v>7.414235197063869</v>
       </c>
       <c r="P10" t="n">
-        <v>269.6698608343377</v>
+        <v>269.6419568989533</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33604,28 +33823,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1110054058481351</v>
+        <v>0.1112846225415523</v>
       </c>
       <c r="J11" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K11" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01060195626628613</v>
+        <v>0.01082704491366493</v>
       </c>
       <c r="M11" t="n">
-        <v>6.13582413870422</v>
+        <v>6.10313363810282</v>
       </c>
       <c r="N11" t="n">
-        <v>61.42431576230677</v>
+        <v>61.0229145734184</v>
       </c>
       <c r="O11" t="n">
-        <v>7.837366634419164</v>
+        <v>7.811716493410293</v>
       </c>
       <c r="P11" t="n">
-        <v>263.9002336651026</v>
+        <v>263.8973105880204</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33676,28 +33895,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05562203631772406</v>
+        <v>-0.05194468990766436</v>
       </c>
       <c r="J12" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K12" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003995824045348928</v>
+        <v>0.003540531366773125</v>
       </c>
       <c r="M12" t="n">
-        <v>5.274884809828441</v>
+        <v>5.258515687648387</v>
       </c>
       <c r="N12" t="n">
-        <v>41.1922583231083</v>
+        <v>40.95753819680801</v>
       </c>
       <c r="O12" t="n">
-        <v>6.418119531693711</v>
+        <v>6.399807668735679</v>
       </c>
       <c r="P12" t="n">
-        <v>264.944434783444</v>
+        <v>264.9061544422323</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33748,28 +33967,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09623305715418952</v>
+        <v>-0.09475308304019875</v>
       </c>
       <c r="J13" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K13" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006795201725059652</v>
+        <v>0.006696813719903716</v>
       </c>
       <c r="M13" t="n">
-        <v>6.613413331541238</v>
+        <v>6.575684671641526</v>
       </c>
       <c r="N13" t="n">
-        <v>72.30228972837608</v>
+        <v>71.82252123358512</v>
       </c>
       <c r="O13" t="n">
-        <v>8.503075310049658</v>
+        <v>8.474816884958939</v>
       </c>
       <c r="P13" t="n">
-        <v>271.2066158508086</v>
+        <v>271.1912201780729</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33820,28 +34039,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.008240899077111393</v>
+        <v>-0.005247348170938734</v>
       </c>
       <c r="J14" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K14" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L14" t="n">
-        <v>5.712271955082837e-05</v>
+        <v>2.353377632635656e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>6.198588961443684</v>
+        <v>6.172550952515413</v>
       </c>
       <c r="N14" t="n">
-        <v>63.50128843681723</v>
+        <v>63.10129286799665</v>
       </c>
       <c r="O14" t="n">
-        <v>7.968769568560583</v>
+        <v>7.943632221345387</v>
       </c>
       <c r="P14" t="n">
-        <v>272.6394274894377</v>
+        <v>272.6082710727093</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33892,28 +34111,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2567058002947259</v>
+        <v>-0.2511018102641049</v>
       </c>
       <c r="J15" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K15" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05099911955396763</v>
+        <v>0.04960122045750504</v>
       </c>
       <c r="M15" t="n">
-        <v>6.038917942801119</v>
+        <v>6.028449617034115</v>
       </c>
       <c r="N15" t="n">
-        <v>65.50015544792559</v>
+        <v>65.15886812756402</v>
       </c>
       <c r="O15" t="n">
-        <v>8.093216631718541</v>
+        <v>8.072104318426765</v>
       </c>
       <c r="P15" t="n">
-        <v>286.5355655531642</v>
+        <v>286.4772325947764</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33964,28 +34183,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4273704607247127</v>
+        <v>-0.4200680036235294</v>
       </c>
       <c r="J16" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K16" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1319758800878265</v>
+        <v>0.1296152203058633</v>
       </c>
       <c r="M16" t="n">
-        <v>6.20566859325702</v>
+        <v>6.19686726291716</v>
       </c>
       <c r="N16" t="n">
-        <v>64.25449488002899</v>
+        <v>63.99288424421054</v>
       </c>
       <c r="O16" t="n">
-        <v>8.015890148949708</v>
+        <v>7.999555252900659</v>
       </c>
       <c r="P16" t="n">
-        <v>287.2841769495738</v>
+        <v>287.2081621848652</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34036,28 +34255,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.210996145624771</v>
+        <v>-0.2003720204373154</v>
       </c>
       <c r="J17" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K17" t="n">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03792924091978989</v>
+        <v>0.03467418872895112</v>
       </c>
       <c r="M17" t="n">
-        <v>6.499499401859097</v>
+        <v>6.509185985934346</v>
       </c>
       <c r="N17" t="n">
-        <v>60.40031353694781</v>
+        <v>60.36413176116544</v>
       </c>
       <c r="O17" t="n">
-        <v>7.771763862659995</v>
+        <v>7.769435742778586</v>
       </c>
       <c r="P17" t="n">
-        <v>279.2942904644973</v>
+        <v>279.1836898897046</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34108,28 +34327,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1928447057101781</v>
+        <v>0.2064569422711515</v>
       </c>
       <c r="J18" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K18" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02754658216969963</v>
+        <v>0.03168280258074974</v>
       </c>
       <c r="M18" t="n">
-        <v>6.482944759184867</v>
+        <v>6.515774395035109</v>
       </c>
       <c r="N18" t="n">
-        <v>70.35415365344218</v>
+        <v>70.48447794547553</v>
       </c>
       <c r="O18" t="n">
-        <v>8.387738291902185</v>
+        <v>8.395503436094558</v>
       </c>
       <c r="P18" t="n">
-        <v>263.978963939934</v>
+        <v>263.8373473765985</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34167,7 +34386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S441"/>
+  <dimension ref="A1:S444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76931,6 +77150,297 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:13:02+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-40.83299437070356,172.87566251871178</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-40.83300368509766,172.87471311974923</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-40.83303527276145,172.87374754075324</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-40.83300699069939,172.8727986859205</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-40.833030769890556,172.87184985934837</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-40.83299888143306,172.87095067159177</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-40.832918287258195,172.87000646972456</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-40.832837873953245,172.8691076749868</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-40.8327073119708,172.8681728198488</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-40.832584756341255,172.86723721697797</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-40.83246543576958,172.86634908061413</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-40.83228623663411,172.865428496773</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-40.83210897026414,172.86452371641516</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-40.831877918650676,172.8636187068687</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-40.83175080195483,172.86268326217998</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-40.83162031293231,172.86172512107996</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>-40.831490149274906,172.86079189715844</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-40.83299428064412,172.875662521531</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-40.83300782783047,172.87471299000654</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-40.83303869598669,172.87374754265446</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-40.83300374764394,172.87279868416556</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-40.83303149056954,172.8718498597281</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-40.832996725340706,172.8709508825343</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-40.83292349816793,172.87000596624569</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-40.83283582112834,172.86910804479476</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-40.832705973005424,172.86817305941946</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-40.832587077201424,172.8672368015955</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-40.83246437515156,172.86634935580904</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-40.83229003717417,172.865427510608</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-40.832107121089734,172.8645242420472</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-40.83187932754234,172.86361830636937</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-40.83175009737237,172.86268346159437</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-40.831606413804884,172.86172856633328</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>-40.83150502219659,172.8607882103152</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-40.8329819425016,172.87566290776243</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-40.83299918212719,172.8747132607739</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-40.83303293055472,172.87374753945238</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-40.83299753178767,172.87279868080194</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-40.833025995392354,172.8718498568328</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-40.83299151478422,172.87095139231195</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-40.83291298650519,172.870006981884</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-40.832820915834546,172.86911072992143</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-40.8326893698346,172.868176030095</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-40.832558423504445,172.8672419299691</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-40.83246128168234,172.86635015846082</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-40.832299582716594,172.86542503372786</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-40.83211460584327,172.86452211448878</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-40.831875981424616,172.86361925755523</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-40.83174437263994,172.8626850818363</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-40.831600305271124,172.8617300804887</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-40.83149785132365,172.86078998790055</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S444"/>
+  <dimension ref="A1:S447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28412,10 +28412,10 @@
         <v>274.02</v>
       </c>
       <c r="O444" t="n">
-        <v>283.86</v>
+        <v>280.11</v>
       </c>
       <c r="P444" t="n">
-        <v>281.53</v>
+        <v>277.11</v>
       </c>
       <c r="Q444" t="n">
         <v>282.13</v>
@@ -28424,6 +28424,195 @@
         <v>278.62</v>
       </c>
       <c r="S444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>263.91</v>
+      </c>
+      <c r="C445" t="n">
+        <v>260.31</v>
+      </c>
+      <c r="D445" t="n">
+        <v>254.93</v>
+      </c>
+      <c r="E445" t="n">
+        <v>258.46</v>
+      </c>
+      <c r="F445" t="n">
+        <v>255.26</v>
+      </c>
+      <c r="G445" t="n">
+        <v>255.01</v>
+      </c>
+      <c r="H445" t="n">
+        <v>257.92</v>
+      </c>
+      <c r="I445" t="n">
+        <v>261.81</v>
+      </c>
+      <c r="J445" t="n">
+        <v>265.14</v>
+      </c>
+      <c r="K445" t="n">
+        <v>268.22</v>
+      </c>
+      <c r="L445" t="n">
+        <v>265.92</v>
+      </c>
+      <c r="M445" t="n">
+        <v>269</v>
+      </c>
+      <c r="N445" t="n">
+        <v>273.93</v>
+      </c>
+      <c r="O445" t="n">
+        <v>280.67</v>
+      </c>
+      <c r="P445" t="n">
+        <v>277.11</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>282.4</v>
+      </c>
+      <c r="R445" t="n">
+        <v>278.51</v>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>264.23</v>
+      </c>
+      <c r="C446" t="n">
+        <v>260.99</v>
+      </c>
+      <c r="D446" t="n">
+        <v>255.41</v>
+      </c>
+      <c r="E446" t="n">
+        <v>258.29</v>
+      </c>
+      <c r="F446" t="n">
+        <v>255.49</v>
+      </c>
+      <c r="G446" t="n">
+        <v>255.47</v>
+      </c>
+      <c r="H446" t="n">
+        <v>258.17</v>
+      </c>
+      <c r="I446" t="n">
+        <v>262.11</v>
+      </c>
+      <c r="J446" t="n">
+        <v>265.76</v>
+      </c>
+      <c r="K446" t="n">
+        <v>268.92</v>
+      </c>
+      <c r="L446" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="M446" t="n">
+        <v>269.79</v>
+      </c>
+      <c r="N446" t="n">
+        <v>274.04</v>
+      </c>
+      <c r="O446" t="n">
+        <v>281.01</v>
+      </c>
+      <c r="P446" t="n">
+        <v>277.49</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>282.73</v>
+      </c>
+      <c r="R446" t="n">
+        <v>276.72</v>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>264.81</v>
+      </c>
+      <c r="C447" t="n">
+        <v>261.81</v>
+      </c>
+      <c r="D447" t="n">
+        <v>256.2</v>
+      </c>
+      <c r="E447" t="n">
+        <v>258.85</v>
+      </c>
+      <c r="F447" t="n">
+        <v>256.25</v>
+      </c>
+      <c r="G447" t="n">
+        <v>256.44</v>
+      </c>
+      <c r="H447" t="n">
+        <v>259.36</v>
+      </c>
+      <c r="I447" t="n">
+        <v>263.08</v>
+      </c>
+      <c r="J447" t="n">
+        <v>266.84</v>
+      </c>
+      <c r="K447" t="n">
+        <v>270.14</v>
+      </c>
+      <c r="L447" t="n">
+        <v>266.98</v>
+      </c>
+      <c r="M447" t="n">
+        <v>270.98</v>
+      </c>
+      <c r="N447" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="O447" t="n">
+        <v>281.41</v>
+      </c>
+      <c r="P447" t="n">
+        <v>278.58</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>284.82</v>
+      </c>
+      <c r="R447" t="n">
+        <v>276.47</v>
+      </c>
+      <c r="S447" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28440,7 +28629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B457"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33013,6 +33202,36 @@
       </c>
       <c r="B457" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -33175,28 +33394,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4356912854564569</v>
+        <v>-0.4332358080587158</v>
       </c>
       <c r="J2" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K2" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2078831302333494</v>
+        <v>0.208599571233646</v>
       </c>
       <c r="M2" t="n">
-        <v>4.523156924940015</v>
+        <v>4.503877118751065</v>
       </c>
       <c r="N2" t="n">
-        <v>39.01109122751026</v>
+        <v>38.76977573866911</v>
       </c>
       <c r="O2" t="n">
-        <v>6.245885944164387</v>
+        <v>6.226538021940371</v>
       </c>
       <c r="P2" t="n">
-        <v>274.158838780056</v>
+        <v>274.133191704053</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33247,28 +33466,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3260684201266394</v>
+        <v>-0.3250159281907498</v>
       </c>
       <c r="J3" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K3" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1044336903763358</v>
+        <v>0.1053347970778492</v>
       </c>
       <c r="M3" t="n">
-        <v>5.157672202620083</v>
+        <v>5.127273315702777</v>
       </c>
       <c r="N3" t="n">
-        <v>49.17393217400938</v>
+        <v>48.84945273707075</v>
       </c>
       <c r="O3" t="n">
-        <v>7.012412721311359</v>
+        <v>6.989238351714065</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9633637197273</v>
+        <v>268.9523633032284</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33319,28 +33538,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3764454966297421</v>
+        <v>-0.3763721187213935</v>
       </c>
       <c r="J4" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K4" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.112592050097906</v>
+        <v>0.1141774419323295</v>
       </c>
       <c r="M4" t="n">
-        <v>5.364787200093733</v>
+        <v>5.331701494201515</v>
       </c>
       <c r="N4" t="n">
-        <v>60.23933060561504</v>
+        <v>59.8360675407557</v>
       </c>
       <c r="O4" t="n">
-        <v>7.761400041591403</v>
+        <v>7.73537765986611</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4767867447653</v>
+        <v>265.4760118885702</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33391,28 +33610,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3040089993517033</v>
+        <v>-0.3017863987155563</v>
       </c>
       <c r="J5" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K5" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08770410701987086</v>
+        <v>0.08779937506460789</v>
       </c>
       <c r="M5" t="n">
-        <v>4.730083864431723</v>
+        <v>4.707666458696318</v>
       </c>
       <c r="N5" t="n">
-        <v>51.8500292105148</v>
+        <v>51.51811864110863</v>
       </c>
       <c r="O5" t="n">
-        <v>7.20069643926994</v>
+        <v>7.177612321734061</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0375255738525</v>
+        <v>265.0143133443576</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33463,28 +33682,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3976019423920919</v>
+        <v>-0.3996443720628135</v>
       </c>
       <c r="J6" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K6" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2138069333734505</v>
+        <v>0.2182018049902192</v>
       </c>
       <c r="M6" t="n">
-        <v>4.264591731664714</v>
+        <v>4.243543875084416</v>
       </c>
       <c r="N6" t="n">
-        <v>31.3519643516739</v>
+        <v>31.15626984326053</v>
       </c>
       <c r="O6" t="n">
-        <v>5.599282485432745</v>
+        <v>5.58178016794468</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6956107020047</v>
+        <v>267.7169314081212</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33535,28 +33754,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6290165601148299</v>
+        <v>-0.629803297430095</v>
       </c>
       <c r="J7" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K7" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.295096816318314</v>
+        <v>0.2989810374809639</v>
       </c>
       <c r="M7" t="n">
-        <v>5.168927767626548</v>
+        <v>5.138715708999962</v>
       </c>
       <c r="N7" t="n">
-        <v>50.9740855385384</v>
+        <v>50.63580404091148</v>
       </c>
       <c r="O7" t="n">
-        <v>7.139613822787505</v>
+        <v>7.11588392548048</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9316868222296</v>
+        <v>272.9398922768411</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33607,28 +33826,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4653104842770403</v>
+        <v>-0.4626366731761464</v>
       </c>
       <c r="J8" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K8" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1913488101348971</v>
+        <v>0.1919879994442383</v>
       </c>
       <c r="M8" t="n">
-        <v>5.231778338245679</v>
+        <v>5.209408980075379</v>
       </c>
       <c r="N8" t="n">
-        <v>49.34935456780887</v>
+        <v>49.04396450021245</v>
       </c>
       <c r="O8" t="n">
-        <v>7.024909577198049</v>
+        <v>7.003139617358236</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9600071930385</v>
+        <v>268.9320762575846</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33679,28 +33898,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1957309273480155</v>
+        <v>-0.1916698878593238</v>
       </c>
       <c r="J9" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K9" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04278818308772647</v>
+        <v>0.04169669760327055</v>
       </c>
       <c r="M9" t="n">
-        <v>5.110997897253712</v>
+        <v>5.096021867422308</v>
       </c>
       <c r="N9" t="n">
-        <v>46.2235663690602</v>
+        <v>45.96961127644426</v>
       </c>
       <c r="O9" t="n">
-        <v>6.79879153740282</v>
+        <v>6.780089326582966</v>
       </c>
       <c r="P9" t="n">
-        <v>264.6455618765343</v>
+        <v>264.6031464870138</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33751,28 +33970,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2810731486862204</v>
+        <v>-0.2758150024118747</v>
       </c>
       <c r="J10" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K10" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07193568922593074</v>
+        <v>0.07039400342456215</v>
       </c>
       <c r="M10" t="n">
-        <v>5.708119066814568</v>
+        <v>5.69781934973471</v>
       </c>
       <c r="N10" t="n">
-        <v>54.97088355738071</v>
+        <v>54.69665287617286</v>
       </c>
       <c r="O10" t="n">
-        <v>7.414235197063869</v>
+        <v>7.395718550362288</v>
       </c>
       <c r="P10" t="n">
-        <v>269.6419568989533</v>
+        <v>269.5870382623673</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33823,28 +34042,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1112846225415523</v>
+        <v>0.1144225380257479</v>
       </c>
       <c r="J11" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K11" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01082704491366493</v>
+        <v>0.01161671731372305</v>
       </c>
       <c r="M11" t="n">
-        <v>6.10313363810282</v>
+        <v>6.077196976348241</v>
       </c>
       <c r="N11" t="n">
-        <v>61.0229145734184</v>
+        <v>60.64944800182194</v>
       </c>
       <c r="O11" t="n">
-        <v>7.811716493410293</v>
+        <v>7.787775549014105</v>
       </c>
       <c r="P11" t="n">
-        <v>263.8973105880204</v>
+        <v>263.8645307354296</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33895,28 +34114,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05194468990766436</v>
+        <v>-0.04784588719241204</v>
       </c>
       <c r="J12" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K12" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003540531366773125</v>
+        <v>0.003050075906481431</v>
       </c>
       <c r="M12" t="n">
-        <v>5.258515687648387</v>
+        <v>5.245004170766048</v>
       </c>
       <c r="N12" t="n">
-        <v>40.95753819680801</v>
+        <v>40.73930821033219</v>
       </c>
       <c r="O12" t="n">
-        <v>6.399807668735679</v>
+        <v>6.382735166864766</v>
       </c>
       <c r="P12" t="n">
-        <v>264.9061544422323</v>
+        <v>264.8633465593864</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33967,28 +34186,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09475308304019875</v>
+        <v>-0.09298936733449904</v>
       </c>
       <c r="J13" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K13" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006696813719903716</v>
+        <v>0.006554695491687301</v>
       </c>
       <c r="M13" t="n">
-        <v>6.575684671641526</v>
+        <v>6.539723704890378</v>
       </c>
       <c r="N13" t="n">
-        <v>71.82252123358512</v>
+        <v>71.35423521846504</v>
       </c>
       <c r="O13" t="n">
-        <v>8.474816884958939</v>
+        <v>8.447143612989247</v>
       </c>
       <c r="P13" t="n">
-        <v>271.1912201780729</v>
+        <v>271.1727897601189</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34039,28 +34258,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.005247348170938734</v>
+        <v>-0.00280486978462671</v>
       </c>
       <c r="J14" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K14" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L14" t="n">
-        <v>2.353377632635656e-05</v>
+        <v>6.831791264705345e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>6.172550952515413</v>
+        <v>6.14398864015697</v>
       </c>
       <c r="N14" t="n">
-        <v>63.10129286799665</v>
+        <v>62.69740722882577</v>
       </c>
       <c r="O14" t="n">
-        <v>7.943632221345387</v>
+        <v>7.918169436733832</v>
       </c>
       <c r="P14" t="n">
-        <v>272.6082710727093</v>
+        <v>272.5827609246898</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34111,28 +34330,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2511018102641049</v>
+        <v>-0.251120363201728</v>
       </c>
       <c r="J15" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K15" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04960122045750504</v>
+        <v>0.05039620895308772</v>
       </c>
       <c r="M15" t="n">
-        <v>6.028449617034115</v>
+        <v>5.987757425691014</v>
       </c>
       <c r="N15" t="n">
-        <v>65.15886812756402</v>
+        <v>64.69491737333797</v>
       </c>
       <c r="O15" t="n">
-        <v>8.072104318426765</v>
+        <v>8.043315073608516</v>
       </c>
       <c r="P15" t="n">
-        <v>286.4772325947764</v>
+        <v>286.4773835015582</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34183,28 +34402,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4200680036235294</v>
+        <v>-0.4197557743053775</v>
       </c>
       <c r="J16" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K16" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1296152203058633</v>
+        <v>0.1313585395120951</v>
       </c>
       <c r="M16" t="n">
-        <v>6.19686726291716</v>
+        <v>6.15644699436923</v>
       </c>
       <c r="N16" t="n">
-        <v>63.99288424421054</v>
+        <v>63.51860758618073</v>
       </c>
       <c r="O16" t="n">
-        <v>7.999555252900659</v>
+        <v>7.969856183531841</v>
       </c>
       <c r="P16" t="n">
-        <v>287.2081621848652</v>
+        <v>287.2048468193465</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34255,28 +34474,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2003720204373154</v>
+        <v>-0.1870889747397326</v>
       </c>
       <c r="J17" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K17" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03467418872895112</v>
+        <v>0.03054930697224623</v>
       </c>
       <c r="M17" t="n">
-        <v>6.509185985934346</v>
+        <v>6.532289963952241</v>
       </c>
       <c r="N17" t="n">
-        <v>60.36413176116544</v>
+        <v>60.55445790141443</v>
       </c>
       <c r="O17" t="n">
-        <v>7.769435742778586</v>
+        <v>7.781674492126642</v>
       </c>
       <c r="P17" t="n">
-        <v>279.1836898897046</v>
+        <v>279.0449673507792</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34327,28 +34546,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2064569422711515</v>
+        <v>0.217552364387327</v>
       </c>
       <c r="J18" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K18" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03168280258074974</v>
+        <v>0.03540398369765607</v>
       </c>
       <c r="M18" t="n">
-        <v>6.515774395035109</v>
+        <v>6.534733638839078</v>
       </c>
       <c r="N18" t="n">
-        <v>70.48447794547553</v>
+        <v>70.42664911060639</v>
       </c>
       <c r="O18" t="n">
-        <v>8.395503436094558</v>
+        <v>8.392058693229355</v>
       </c>
       <c r="P18" t="n">
-        <v>263.8373473765985</v>
+        <v>263.7215486947888</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34386,7 +34605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S444"/>
+  <dimension ref="A1:S447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77417,12 +77636,12 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>-40.831875981424616,172.86361925755523</t>
+          <t>-40.8319090023228,172.8636098708486</t>
         </is>
       </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>-40.83174437263994,172.8626850818363</t>
+          <t>-40.831783300819986,172.86267406418574</t>
         </is>
       </c>
       <c r="Q444" t="inlineStr">
@@ -77436,6 +77655,297 @@
         </is>
       </c>
       <c r="S444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-40.832978430183644,172.87566301771147</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-40.83299359844383,172.87471343564442</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-40.83302716512273,172.8737475362503</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-40.832995369750705,172.87279867963198</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-40.83302419369493,172.8718498558835</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-40.832991694458585,172.87095137473344</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-40.832912447445565,172.870007033968</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-40.83281788122381,172.86911127659377</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-40.83269088732872,172.8681757585817</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-40.83256618945975,172.8672405400365</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-40.83246481707573,172.8663492411445</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-40.8322980801775,172.86542542360718</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-40.83211539834659,172.86452188921785</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-40.83190407120206,172.86361127259738</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-40.831783300819986,172.86267406418574</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-40.8315979149753,172.86173067298427</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-40.83149882514591,172.86078974650007</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-40.83297554828174,172.8756631079261</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-40.832987474403986,172.87471362743784</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-40.83302284104875,172.87374753384876</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-40.83299690119355,172.8727986804607</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-40.83302212174288,172.87184985479186</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-40.83298756194826,172.8709517790398</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-40.83291020136378,172.87000725098468</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-40.832815203626105,172.86911175895168</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-40.83268535293841,172.86817674880658</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-40.83255994098996,172.86724165837313</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-40.83246030944917,172.8663504107228</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-40.832291097790005,172.8654272353991</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-40.83211442973143,172.864522164549</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-40.83190107730732,172.86361212365904</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-40.83177995405344,172.86267501140506</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-40.83159499350262,172.8617313971454</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-40.83151467188974,172.8607858182553</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-40.83297032483453,172.87566327144006</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-40.832980089532406,172.87471385871814</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-40.833015724343646,172.87374752989624</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-40.83299185644063,172.87279867773083</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-40.83301527529263,172.8718498511846</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-40.83297884774167,172.87095263159875</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-40.83289951001447,172.87000828398385</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-40.83280654606017,172.8691133185753</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-40.83267571238755,172.86817847371404</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-40.83254905079974,172.86724360747354</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-40.832455448283234,172.86635167203255</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-40.83228058001635,172.8654299645533</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-40.832109058320064,172.86452369138507</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-40.83189755507821,172.86361312490797</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-40.83177035411773,172.86267772842842</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-40.83157649084218,172.86173598349788</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>-40.831516885122106,172.86078526961762</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S447"/>
+  <dimension ref="A1:S448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28613,6 +28613,69 @@
         <v>276.47</v>
       </c>
       <c r="S447" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>264.68</v>
+      </c>
+      <c r="C448" t="n">
+        <v>262.46</v>
+      </c>
+      <c r="D448" t="n">
+        <v>256.42</v>
+      </c>
+      <c r="E448" t="n">
+        <v>258.13</v>
+      </c>
+      <c r="F448" t="n">
+        <v>255.78</v>
+      </c>
+      <c r="G448" t="n">
+        <v>256.11</v>
+      </c>
+      <c r="H448" t="n">
+        <v>258.8</v>
+      </c>
+      <c r="I448" t="n">
+        <v>262.07</v>
+      </c>
+      <c r="J448" t="n">
+        <v>265.22</v>
+      </c>
+      <c r="K448" t="n">
+        <v>267.44</v>
+      </c>
+      <c r="L448" t="n">
+        <v>264.14</v>
+      </c>
+      <c r="M448" t="n">
+        <v>270.31</v>
+      </c>
+      <c r="N448" t="n">
+        <v>273.24</v>
+      </c>
+      <c r="O448" t="n">
+        <v>280.69</v>
+      </c>
+      <c r="P448" t="n">
+        <v>277.09</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>285.62</v>
+      </c>
+      <c r="R448" t="n">
+        <v>276.84</v>
+      </c>
+      <c r="S448" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28629,7 +28692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B460"/>
+  <dimension ref="A1:B461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33232,6 +33295,16 @@
       </c>
       <c r="B460" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>
@@ -33394,28 +33467,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4332358080587158</v>
+        <v>-0.4322510179508536</v>
       </c>
       <c r="J2" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K2" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.208599571233646</v>
+        <v>0.2086922490009699</v>
       </c>
       <c r="M2" t="n">
-        <v>4.503877118751065</v>
+        <v>4.498229775949292</v>
       </c>
       <c r="N2" t="n">
-        <v>38.76977573866911</v>
+        <v>38.69288489541398</v>
       </c>
       <c r="O2" t="n">
-        <v>6.226538021940371</v>
+        <v>6.220360511691744</v>
       </c>
       <c r="P2" t="n">
-        <v>274.133191704053</v>
+        <v>274.1228751200257</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33466,28 +33539,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3250159281907498</v>
+        <v>-0.3239989683384711</v>
       </c>
       <c r="J3" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K3" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1053347970778492</v>
+        <v>0.1052296767243297</v>
       </c>
       <c r="M3" t="n">
-        <v>5.127273315702777</v>
+        <v>5.11998558964614</v>
       </c>
       <c r="N3" t="n">
-        <v>48.84945273707075</v>
+        <v>48.75066582159781</v>
       </c>
       <c r="O3" t="n">
-        <v>6.989238351714065</v>
+        <v>6.982167702196633</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9523633032284</v>
+        <v>268.9417097114785</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33538,28 +33611,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3763721187213935</v>
+        <v>-0.3759096831187093</v>
       </c>
       <c r="J4" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K4" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1141774419323295</v>
+        <v>0.1144682300860759</v>
       </c>
       <c r="M4" t="n">
-        <v>5.331701494201515</v>
+        <v>5.321806532593327</v>
       </c>
       <c r="N4" t="n">
-        <v>59.8360675407557</v>
+        <v>59.70437638207911</v>
       </c>
       <c r="O4" t="n">
-        <v>7.73537765986611</v>
+        <v>7.726860706786367</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4760118885702</v>
+        <v>265.4711674494208</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33610,28 +33683,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3017863987155563</v>
+        <v>-0.3012407418987427</v>
       </c>
       <c r="J5" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K5" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08779937506460789</v>
+        <v>0.08793473058748069</v>
       </c>
       <c r="M5" t="n">
-        <v>4.707666458696318</v>
+        <v>4.699430420955225</v>
       </c>
       <c r="N5" t="n">
-        <v>51.51811864110863</v>
+        <v>51.40588730057291</v>
       </c>
       <c r="O5" t="n">
-        <v>7.177612321734061</v>
+        <v>7.169789906306384</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0143133443576</v>
+        <v>265.0085970862882</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33682,28 +33755,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3996443720628135</v>
+        <v>-0.4002394868861847</v>
       </c>
       <c r="J6" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K6" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2182018049902192</v>
+        <v>0.2196085824551859</v>
       </c>
       <c r="M6" t="n">
-        <v>4.243543875084416</v>
+        <v>4.236270774893954</v>
       </c>
       <c r="N6" t="n">
-        <v>31.15626984326053</v>
+        <v>31.09016333613807</v>
       </c>
       <c r="O6" t="n">
-        <v>5.58178016794468</v>
+        <v>5.575855390533193</v>
       </c>
       <c r="P6" t="n">
-        <v>267.7169314081212</v>
+        <v>267.7231657843932</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33754,28 +33827,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.629803297430095</v>
+        <v>-0.6298177816828286</v>
       </c>
       <c r="J7" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K7" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2989810374809639</v>
+        <v>0.3001167974674203</v>
       </c>
       <c r="M7" t="n">
-        <v>5.138715708999962</v>
+        <v>5.127281429535696</v>
       </c>
       <c r="N7" t="n">
-        <v>50.63580404091148</v>
+        <v>50.52252696639621</v>
       </c>
       <c r="O7" t="n">
-        <v>7.11588392548048</v>
+        <v>7.107920016882309</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9398922768411</v>
+        <v>272.9400440127382</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33826,28 +33899,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4626366731761464</v>
+        <v>-0.4616017491008677</v>
       </c>
       <c r="J8" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K8" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1919879994442383</v>
+        <v>0.192091326985777</v>
       </c>
       <c r="M8" t="n">
-        <v>5.209408980075379</v>
+        <v>5.202680580087128</v>
       </c>
       <c r="N8" t="n">
-        <v>49.04396450021245</v>
+        <v>48.94511652569477</v>
       </c>
       <c r="O8" t="n">
-        <v>7.003139617358236</v>
+        <v>6.996078653481161</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9320762575846</v>
+        <v>268.9212344740416</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33898,28 +33971,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1916698878593238</v>
+        <v>-0.1904618221989251</v>
       </c>
       <c r="J9" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K9" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04169669760327055</v>
+        <v>0.04139401750209692</v>
       </c>
       <c r="M9" t="n">
-        <v>5.096021867422308</v>
+        <v>5.090409892864113</v>
       </c>
       <c r="N9" t="n">
-        <v>45.96961127644426</v>
+        <v>45.88158238972349</v>
       </c>
       <c r="O9" t="n">
-        <v>6.780089326582966</v>
+        <v>6.773594495518867</v>
       </c>
       <c r="P9" t="n">
-        <v>264.6031464870138</v>
+        <v>264.590490885788</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33970,28 +34043,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2758150024118747</v>
+        <v>-0.2744181520685329</v>
       </c>
       <c r="J10" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K10" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07039400342456215</v>
+        <v>0.0700577177801559</v>
       </c>
       <c r="M10" t="n">
-        <v>5.69781934973471</v>
+        <v>5.692516533724885</v>
       </c>
       <c r="N10" t="n">
-        <v>54.69665287617286</v>
+        <v>54.59409127021345</v>
       </c>
       <c r="O10" t="n">
-        <v>7.395718550362288</v>
+        <v>7.388781446910813</v>
       </c>
       <c r="P10" t="n">
-        <v>269.5870382623673</v>
+        <v>269.5724049675913</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34042,28 +34115,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1144225380257479</v>
+        <v>0.1146652611189163</v>
       </c>
       <c r="J11" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K11" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01161671731372305</v>
+        <v>0.01172740606913403</v>
       </c>
       <c r="M11" t="n">
-        <v>6.077196976348241</v>
+        <v>6.064760727682099</v>
       </c>
       <c r="N11" t="n">
-        <v>60.64944800182194</v>
+        <v>60.51436482231828</v>
       </c>
       <c r="O11" t="n">
-        <v>7.787775549014105</v>
+        <v>7.779097943998281</v>
       </c>
       <c r="P11" t="n">
-        <v>263.8645307354296</v>
+        <v>263.8619879873191</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34114,28 +34187,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04784588719241204</v>
+        <v>-0.04758860897406814</v>
       </c>
       <c r="J12" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K12" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003050075906481431</v>
+        <v>0.003033600179552121</v>
       </c>
       <c r="M12" t="n">
-        <v>5.245004170766048</v>
+        <v>5.234634295940563</v>
       </c>
       <c r="N12" t="n">
-        <v>40.73930821033219</v>
+        <v>40.64884058939879</v>
       </c>
       <c r="O12" t="n">
-        <v>6.382735166864766</v>
+        <v>6.375644327391451</v>
       </c>
       <c r="P12" t="n">
-        <v>264.8633465593864</v>
+        <v>264.8606513329247</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34186,28 +34259,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09298936733449904</v>
+        <v>-0.09223355594383208</v>
       </c>
       <c r="J13" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K13" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006554695491687301</v>
+        <v>0.00648321790774109</v>
       </c>
       <c r="M13" t="n">
-        <v>6.539723704890378</v>
+        <v>6.528620239242686</v>
       </c>
       <c r="N13" t="n">
-        <v>71.35423521846504</v>
+        <v>71.2004035748445</v>
       </c>
       <c r="O13" t="n">
-        <v>8.447143612989247</v>
+        <v>8.438033157960717</v>
       </c>
       <c r="P13" t="n">
-        <v>271.1727897601189</v>
+        <v>271.164871939196</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34258,28 +34331,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.00280486978462671</v>
+        <v>-0.002464805621526992</v>
       </c>
       <c r="J14" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K14" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L14" t="n">
-        <v>6.831791264705345e-06</v>
+        <v>5.303931967626241e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>6.14398864015697</v>
+        <v>6.132032625992668</v>
       </c>
       <c r="N14" t="n">
-        <v>62.69740722882577</v>
+        <v>62.55831821842001</v>
       </c>
       <c r="O14" t="n">
-        <v>7.918169436733832</v>
+        <v>7.909381658411738</v>
       </c>
       <c r="P14" t="n">
-        <v>272.5827609246898</v>
+        <v>272.5791984391558</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34330,28 +34403,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.251120363201728</v>
+        <v>-0.250691505338469</v>
       </c>
       <c r="J15" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K15" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05039620895308772</v>
+        <v>0.05048815810539176</v>
       </c>
       <c r="M15" t="n">
-        <v>5.987757425691014</v>
+        <v>5.976641244810611</v>
       </c>
       <c r="N15" t="n">
-        <v>64.69491737333797</v>
+        <v>64.55205257471519</v>
       </c>
       <c r="O15" t="n">
-        <v>8.043315073608516</v>
+        <v>8.034429200305096</v>
       </c>
       <c r="P15" t="n">
-        <v>286.4773835015582</v>
+        <v>286.4728908201768</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34402,28 +34475,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4197557743053775</v>
+        <v>-0.4192509892415048</v>
       </c>
       <c r="J16" t="n">
+        <v>447</v>
+      </c>
+      <c r="K16" t="n">
         <v>446</v>
       </c>
-      <c r="K16" t="n">
-        <v>445</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1313585395120951</v>
+        <v>0.1316914610307794</v>
       </c>
       <c r="M16" t="n">
-        <v>6.15644699436923</v>
+        <v>6.144895680065368</v>
       </c>
       <c r="N16" t="n">
-        <v>63.51860758618073</v>
+        <v>63.37878094817107</v>
       </c>
       <c r="O16" t="n">
-        <v>7.969856183531841</v>
+        <v>7.961079132138498</v>
       </c>
       <c r="P16" t="n">
-        <v>287.2048468193465</v>
+        <v>287.1995586806001</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34474,28 +34547,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1870889747397326</v>
+        <v>-0.1816792242962622</v>
       </c>
       <c r="J17" t="n">
+        <v>447</v>
+      </c>
+      <c r="K17" t="n">
         <v>446</v>
       </c>
-      <c r="K17" t="n">
-        <v>445</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.03054930697224623</v>
+        <v>0.02887094568319515</v>
       </c>
       <c r="M17" t="n">
-        <v>6.532289963952241</v>
+        <v>6.544834705938847</v>
       </c>
       <c r="N17" t="n">
-        <v>60.55445790141443</v>
+        <v>60.71635692102478</v>
       </c>
       <c r="O17" t="n">
-        <v>7.781674492126642</v>
+        <v>7.79207013065365</v>
       </c>
       <c r="P17" t="n">
-        <v>279.0449673507792</v>
+        <v>278.9882946934933</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34546,28 +34619,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.217552364387327</v>
+        <v>0.2209723852914758</v>
       </c>
       <c r="J18" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K18" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03540398369765607</v>
+        <v>0.03661386459761695</v>
       </c>
       <c r="M18" t="n">
-        <v>6.534733638839078</v>
+        <v>6.53949317326833</v>
       </c>
       <c r="N18" t="n">
-        <v>70.42664911060639</v>
+        <v>70.3876742234014</v>
       </c>
       <c r="O18" t="n">
-        <v>8.392058693229355</v>
+        <v>8.389736242779113</v>
       </c>
       <c r="P18" t="n">
-        <v>263.7215486947888</v>
+        <v>263.6857357582942</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34605,7 +34678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S447"/>
+  <dimension ref="A1:S448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77951,6 +78024,103 @@
         </is>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-40.832971495607175,172.87566323479035</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-40.83297423567078,172.87471404205004</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-40.833013742476396,172.8737475287955</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-40.832998342551534,172.87279868124068</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-40.83301950928159,172.8718498534154</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-40.832981812368665,172.87095234155296</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-40.83290454123768,172.87000779786663</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-40.83281556063915,172.8691116946373</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-40.832690173213834,172.86817588635267</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-40.83257315204033,172.8672392938898</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-40.832480549576196,172.86634515908568</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-40.83228650178809,172.8654284279708</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-40.832121474205294,172.86452016214062</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-40.831903895090605,172.86361132265984</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-40.8317834769656,172.8626740143321</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>-40.83156940848404,172.86173773903883</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>-40.8315136095382,172.86078608160136</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0571/nzd0571.xlsx
+++ b/data/nzd0571/nzd0571.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S448"/>
+  <dimension ref="A1:S449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28676,6 +28676,69 @@
         <v>276.84</v>
       </c>
       <c r="S448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>264.4</v>
+      </c>
+      <c r="C449" t="n">
+        <v>262.17</v>
+      </c>
+      <c r="D449" t="n">
+        <v>256.64</v>
+      </c>
+      <c r="E449" t="n">
+        <v>257.82</v>
+      </c>
+      <c r="F449" t="n">
+        <v>255.66</v>
+      </c>
+      <c r="G449" t="n">
+        <v>256.18</v>
+      </c>
+      <c r="H449" t="n">
+        <v>260.14</v>
+      </c>
+      <c r="I449" t="n">
+        <v>263.81</v>
+      </c>
+      <c r="J449" t="n">
+        <v>266.13</v>
+      </c>
+      <c r="K449" t="n">
+        <v>267.72</v>
+      </c>
+      <c r="L449" t="n">
+        <v>263.75</v>
+      </c>
+      <c r="M449" t="n">
+        <v>269.68</v>
+      </c>
+      <c r="N449" t="n">
+        <v>272.21</v>
+      </c>
+      <c r="O449" t="n">
+        <v>278.6</v>
+      </c>
+      <c r="P449" t="n">
+        <v>275.81</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>285.91</v>
+      </c>
+      <c r="R449" t="n">
+        <v>276.68</v>
+      </c>
+      <c r="S449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28692,7 +28755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33305,6 +33368,16 @@
       </c>
       <c r="B461" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -33467,28 +33540,28 @@
         <v>0.0407</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4322510179508536</v>
+        <v>-0.4313771325868206</v>
       </c>
       <c r="J2" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K2" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2086922490009699</v>
+        <v>0.2088890142089811</v>
       </c>
       <c r="M2" t="n">
-        <v>4.498229775949292</v>
+        <v>4.492061416720775</v>
       </c>
       <c r="N2" t="n">
-        <v>38.69288489541398</v>
+        <v>38.61419134128133</v>
       </c>
       <c r="O2" t="n">
-        <v>6.220360511691744</v>
+        <v>6.214031810449745</v>
       </c>
       <c r="P2" t="n">
-        <v>274.1228751200257</v>
+        <v>274.1136728070273</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33539,28 +33612,28 @@
         <v>0.0375</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3239989683384711</v>
+        <v>-0.3230997153860037</v>
       </c>
       <c r="J3" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K3" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1052296767243297</v>
+        <v>0.1052025285398661</v>
       </c>
       <c r="M3" t="n">
-        <v>5.11998558964614</v>
+        <v>5.112211721569904</v>
       </c>
       <c r="N3" t="n">
-        <v>48.75066582159781</v>
+        <v>48.64997388869316</v>
       </c>
       <c r="O3" t="n">
-        <v>6.982167702196633</v>
+        <v>6.974953325198181</v>
       </c>
       <c r="P3" t="n">
-        <v>268.9417097114785</v>
+        <v>268.932240269062</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33611,28 +33684,28 @@
         <v>0.0406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3759096831187093</v>
+        <v>-0.3753225372624741</v>
       </c>
       <c r="J4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1144682300860759</v>
+        <v>0.1146967949893415</v>
       </c>
       <c r="M4" t="n">
-        <v>5.321806532593327</v>
+        <v>5.31247262695894</v>
       </c>
       <c r="N4" t="n">
-        <v>59.70437638207911</v>
+        <v>59.57457212233356</v>
       </c>
       <c r="O4" t="n">
-        <v>7.726860706786367</v>
+        <v>7.71845658939231</v>
       </c>
       <c r="P4" t="n">
-        <v>265.4711674494208</v>
+        <v>265.4649846019134</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33683,28 +33756,28 @@
         <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3012407418987427</v>
+        <v>-0.30082459861185</v>
       </c>
       <c r="J5" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08793473058748069</v>
+        <v>0.08814658789890784</v>
       </c>
       <c r="M5" t="n">
-        <v>4.699430420955225</v>
+        <v>4.690663625459467</v>
       </c>
       <c r="N5" t="n">
-        <v>51.40588730057291</v>
+        <v>51.29288232604107</v>
       </c>
       <c r="O5" t="n">
-        <v>7.169789906306384</v>
+        <v>7.161904936959235</v>
       </c>
       <c r="P5" t="n">
-        <v>265.0085970862882</v>
+        <v>265.0042149545627</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33755,28 +33828,28 @@
         <v>0.0404</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4002394868861847</v>
+        <v>-0.4008634983829556</v>
       </c>
       <c r="J6" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K6" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2196085824551859</v>
+        <v>0.2210562182807916</v>
       </c>
       <c r="M6" t="n">
-        <v>4.236270774893954</v>
+        <v>4.229109816973027</v>
       </c>
       <c r="N6" t="n">
-        <v>31.09016333613807</v>
+        <v>31.02467879490838</v>
       </c>
       <c r="O6" t="n">
-        <v>5.575855390533193</v>
+        <v>5.569980143134119</v>
       </c>
       <c r="P6" t="n">
-        <v>267.7231657843932</v>
+        <v>267.7297368397561</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33827,28 +33900,28 @@
         <v>0.0404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6298177816828286</v>
+        <v>-0.6297582680071442</v>
       </c>
       <c r="J7" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K7" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3001167974674203</v>
+        <v>0.3012202077657963</v>
       </c>
       <c r="M7" t="n">
-        <v>5.127281429535696</v>
+        <v>5.116147951004386</v>
       </c>
       <c r="N7" t="n">
-        <v>50.52252696639621</v>
+        <v>50.4097890624974</v>
       </c>
       <c r="O7" t="n">
-        <v>7.107920016882309</v>
+        <v>7.099985145230757</v>
       </c>
       <c r="P7" t="n">
-        <v>272.9400440127382</v>
+        <v>272.9394173132947</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33899,28 +33972,28 @@
         <v>0.0415</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4616017491008677</v>
+        <v>-0.4599140034175053</v>
       </c>
       <c r="J8" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K8" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L8" t="n">
-        <v>0.192091326985777</v>
+        <v>0.1917075838542841</v>
       </c>
       <c r="M8" t="n">
-        <v>5.202680580087128</v>
+        <v>5.199034037857801</v>
       </c>
       <c r="N8" t="n">
-        <v>48.94511652569477</v>
+        <v>48.86448964323002</v>
       </c>
       <c r="O8" t="n">
-        <v>6.996078653481161</v>
+        <v>6.990313987456502</v>
       </c>
       <c r="P8" t="n">
-        <v>268.9212344740416</v>
+        <v>268.9034619323799</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33971,28 +34044,28 @@
         <v>0.0405</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1904618221989251</v>
+        <v>-0.1884310009222113</v>
       </c>
       <c r="J9" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K9" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04139401750209692</v>
+        <v>0.04072830385016124</v>
       </c>
       <c r="M9" t="n">
-        <v>5.090409892864113</v>
+        <v>5.088765516262894</v>
       </c>
       <c r="N9" t="n">
-        <v>45.88158238972349</v>
+        <v>45.82061428856033</v>
       </c>
       <c r="O9" t="n">
-        <v>6.773594495518867</v>
+        <v>6.769092574973423</v>
       </c>
       <c r="P9" t="n">
-        <v>264.590490885788</v>
+        <v>264.5691056403071</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34043,28 +34116,28 @@
         <v>0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2744181520685329</v>
+        <v>-0.2725789410827575</v>
       </c>
       <c r="J10" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K10" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0700577177801559</v>
+        <v>0.06949716637900116</v>
       </c>
       <c r="M10" t="n">
-        <v>5.692516533724885</v>
+        <v>5.689524733552438</v>
       </c>
       <c r="N10" t="n">
-        <v>54.59409127021345</v>
+        <v>54.50622358220004</v>
       </c>
       <c r="O10" t="n">
-        <v>7.388781446910813</v>
+        <v>7.382833032258013</v>
       </c>
       <c r="P10" t="n">
-        <v>269.5724049675913</v>
+        <v>269.5530374442779</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34115,28 +34188,28 @@
         <v>0.0356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1146652611189163</v>
+        <v>0.1150309675460206</v>
       </c>
       <c r="J11" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K11" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01172740606913403</v>
+        <v>0.01186476569049311</v>
       </c>
       <c r="M11" t="n">
-        <v>6.064760727682099</v>
+        <v>6.052945721198204</v>
       </c>
       <c r="N11" t="n">
-        <v>60.51436482231828</v>
+        <v>60.38063213571172</v>
       </c>
       <c r="O11" t="n">
-        <v>7.779097943998281</v>
+        <v>7.770497547500528</v>
       </c>
       <c r="P11" t="n">
-        <v>263.8619879873191</v>
+        <v>263.8581369730485</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34187,28 +34260,28 @@
         <v>0.0356</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04758860897406814</v>
+        <v>-0.04751201040517419</v>
       </c>
       <c r="J12" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K12" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003033600179552121</v>
+        <v>0.003040303948092737</v>
       </c>
       <c r="M12" t="n">
-        <v>5.234634295940563</v>
+        <v>5.223350843196447</v>
       </c>
       <c r="N12" t="n">
-        <v>40.64884058939879</v>
+        <v>40.55816553356197</v>
       </c>
       <c r="O12" t="n">
-        <v>6.375644327391451</v>
+        <v>6.368529306956353</v>
       </c>
       <c r="P12" t="n">
-        <v>264.8606513329247</v>
+        <v>264.8598447236883</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34259,28 +34332,28 @@
         <v>0.0309</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09223355594383208</v>
+        <v>-0.09176931631376087</v>
       </c>
       <c r="J13" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K13" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00648321790774109</v>
+        <v>0.006453109683928648</v>
       </c>
       <c r="M13" t="n">
-        <v>6.528620239242686</v>
+        <v>6.516197909497812</v>
       </c>
       <c r="N13" t="n">
-        <v>71.2004035748445</v>
+        <v>71.04363993653337</v>
       </c>
       <c r="O13" t="n">
-        <v>8.438033157960717</v>
+        <v>8.428738929195362</v>
       </c>
       <c r="P13" t="n">
-        <v>271.164871939196</v>
+        <v>271.1599833364593</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34331,28 +34404,28 @@
         <v>0.0304</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.002464805621526992</v>
+        <v>-0.002608994542351515</v>
       </c>
       <c r="J14" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K14" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L14" t="n">
-        <v>5.303931967626241e-06</v>
+        <v>5.975009624958894e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>6.132032625992668</v>
+        <v>6.118956879519694</v>
       </c>
       <c r="N14" t="n">
-        <v>62.55831821842001</v>
+        <v>62.41888804704037</v>
       </c>
       <c r="O14" t="n">
-        <v>7.909381658411738</v>
+        <v>7.900562514596057</v>
       </c>
       <c r="P14" t="n">
-        <v>272.5791984391558</v>
+        <v>272.5807167980103</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34403,28 +34476,28 @@
         <v>0.0251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.250691505338469</v>
+        <v>-0.2512342775820528</v>
       </c>
       <c r="J15" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K15" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05048815810539176</v>
+        <v>0.05095601865788468</v>
       </c>
       <c r="M15" t="n">
-        <v>5.976641244810611</v>
+        <v>5.965573258573875</v>
       </c>
       <c r="N15" t="n">
-        <v>64.55205257471519</v>
+        <v>64.41092374615891</v>
       </c>
       <c r="O15" t="n">
-        <v>8.034429200305096</v>
+        <v>8.025641640776076</v>
       </c>
       <c r="P15" t="n">
-        <v>286.4728908201768</v>
+        <v>286.478606398304</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34475,28 +34548,28 @@
         <v>0.0256</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4192509892415048</v>
+        <v>-0.4193199320592366</v>
       </c>
       <c r="J16" t="n">
+        <v>448</v>
+      </c>
+      <c r="K16" t="n">
         <v>447</v>
       </c>
-      <c r="K16" t="n">
-        <v>446</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1316914610307794</v>
+        <v>0.1323515624998317</v>
       </c>
       <c r="M16" t="n">
-        <v>6.144895680065368</v>
+        <v>6.131497139567588</v>
       </c>
       <c r="N16" t="n">
-        <v>63.37878094817107</v>
+        <v>63.23704183741606</v>
       </c>
       <c r="O16" t="n">
-        <v>7.961079132138498</v>
+        <v>7.952172145861535</v>
       </c>
       <c r="P16" t="n">
-        <v>287.1995586806001</v>
+        <v>287.2002846908779</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34547,28 +34620,28 @@
         <v>0.0307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1816792242962622</v>
+        <v>-0.1761432312036731</v>
       </c>
       <c r="J17" t="n">
+        <v>448</v>
+      </c>
+      <c r="K17" t="n">
         <v>447</v>
       </c>
-      <c r="K17" t="n">
-        <v>446</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.02887094568319515</v>
+        <v>0.02719465026782275</v>
       </c>
       <c r="M17" t="n">
-        <v>6.544834705938847</v>
+        <v>6.557662990847327</v>
       </c>
       <c r="N17" t="n">
-        <v>60.71635692102478</v>
+        <v>60.88919131382517</v>
       </c>
       <c r="O17" t="n">
-        <v>7.79207013065365</v>
+        <v>7.803152652218536</v>
       </c>
       <c r="P17" t="n">
-        <v>278.9882946934933</v>
+        <v>278.9299972810141</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34619,28 +34692,28 @@
         <v>0.0496</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2209723852914758</v>
+        <v>0.2242901147459413</v>
       </c>
       <c r="J18" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K18" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03661386459761695</v>
+        <v>0.0378195556667309</v>
       </c>
       <c r="M18" t="n">
-        <v>6.53949317326833</v>
+        <v>6.543459630308737</v>
       </c>
       <c r="N18" t="n">
-        <v>70.3876742234014</v>
+        <v>70.3410081300806</v>
       </c>
       <c r="O18" t="n">
-        <v>8.389736242779113</v>
+        <v>8.386954639801065</v>
       </c>
       <c r="P18" t="n">
-        <v>263.6857357582942</v>
+        <v>263.6508122832229</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34678,7 +34751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S448"/>
+  <dimension ref="A1:S449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78121,6 +78194,103 @@
         </is>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-40.83297401727134,172.8756631558526</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-40.83297684739365,172.8747139602558</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-40.83301176060914,172.8737475276948</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-40.83300113518261,172.87279868275186</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-40.83302059030007,172.87184985398497</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-40.83298118350839,172.8709524030778</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-40.83289250223929,172.87000896107557</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-40.83280003057238,172.86911449231243</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-40.8326820501571,172.86817733974715</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-40.832570652652436,172.86723974122455</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-40.8324839965847,172.86634426470175</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-40.832292070021175,172.8654269831243</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-40.83213054396536,172.86451758403925</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-40.83192229873752,172.86360609113208</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-40.83179475028446,172.8626708236978</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>-40.831566841129224,172.86173837542233</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>-40.83151502600691,172.86078573047328</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
